--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zaglebie</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -801,22 +801,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cracovia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20</v>
+      </c>
+      <c r="N7" t="n">
+        <v>18</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -859,22 +859,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Widzew Lodz</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -917,22 +917,62 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Piast</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M9" t="n">
+        <v>23</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -975,22 +975,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lech</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -1033,22 +1033,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Motor Lublin</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -1091,22 +1091,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wisla Plock</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M12" t="n">
+        <v>16</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>

--- a/new-stats/radomiak-radom.xlsx
+++ b/new-stats/radomiak-radom.xlsx
@@ -1149,22 +1149,62 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
